--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="96">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -292,6 +292,18 @@
   </si>
   <si>
     <t>REMARKS (-10)</t>
+  </si>
+  <si>
+    <t>PrescriptionRefillRequest5243.dateProcessed</t>
+  </si>
+  <si>
+    <t>DATE PROCESSED (-5)</t>
+  </si>
+  <si>
+    <t>PrescriptionRefillRequest5243.loginDate</t>
+  </si>
+  <si>
+    <t>LOGIN DATE (-11)</t>
   </si>
 </sst>
 </file>
@@ -593,11 +605,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ7"/>
+  <dimension ref="A1:AJ9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.53515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.53515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.73828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.73828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -627,7 +639,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.53515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.73828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1341,6 +1353,206 @@
         <v>72</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>PrescriptionRefillRequest5243.patient</t>
+    <t>PrescriptionRefillRequest5243.rx</t>
   </si>
   <si>
     <t>1</t>
@@ -257,13 +257,13 @@
 </t>
   </si>
   <si>
+    <t>RX # (-3)</t>
+  </si>
+  <si>
+    <t>PrescriptionRefillRequest5243.patient</t>
+  </si>
+  <si>
     <t>PATIENT (-9)</t>
-  </si>
-  <si>
-    <t>PrescriptionRefillRequest5243.rx</t>
-  </si>
-  <si>
-    <t>Rx# (-3)</t>
   </si>
   <si>
     <t>PrescriptionRefillRequest5243.institution</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file PRESCRIPTION REFILL REQUEST (52.43)</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the source PRESCRIPTION REFILL REQUEST (52.43)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>PrescriptionRefillRequest5243.rx</t>
+    <t>PrescriptionRefillRequest5243.patient</t>
   </si>
   <si>
     <t>1</t>
@@ -257,13 +257,13 @@
 </t>
   </si>
   <si>
+    <t>PATIENT (-9)</t>
+  </si>
+  <si>
+    <t>PrescriptionRefillRequest5243.rx</t>
+  </si>
+  <si>
     <t>RX # (-3)</t>
-  </si>
-  <si>
-    <t>PrescriptionRefillRequest5243.patient</t>
-  </si>
-  <si>
-    <t>PATIENT (-9)</t>
   </si>
   <si>
     <t>PrescriptionRefillRequest5243.institution</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFRefillRequestStatus-vista</t>
+    <t>http://va.gov/fhir/ValueSet/RefillRequestStatus-vista</t>
   </si>
   <si>
     <t>PrescriptionRefillRequest5243.remarks</t>
@@ -633,7 +633,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.66015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
+++ b/docs/StructureDefinition-PrescriptionRefillRequest5243.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
